--- a/artfynd/A 11874-2023 artfynd.xlsx
+++ b/artfynd/A 11874-2023 artfynd.xlsx
@@ -1648,7 +1648,7 @@
         <v>92289603</v>
       </c>
       <c r="B10" t="n">
-        <v>84312</v>
+        <v>84314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11874-2023 artfynd.xlsx
+++ b/artfynd/A 11874-2023 artfynd.xlsx
@@ -1648,7 +1648,7 @@
         <v>92289603</v>
       </c>
       <c r="B10" t="n">
-        <v>84314</v>
+        <v>84318</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
